--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T11:56:44+00:00</t>
+    <t>2025-02-18T15:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:23:31+00:00</t>
+    <t>2025-02-20T16:18:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:18:31+00:00</t>
+    <t>2025-02-20T16:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:32:32+00:00</t>
+    <t>2025-02-20T17:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T17:12:55+00:00</t>
+    <t>2025-02-24T09:51:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="128">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T09:51:08+00:00</t>
+    <t>2025-02-25T09:09:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,10 +311,6 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
-</t>
   </si>
   <si>
     <t>Custodian.typeId.nullFlavor</t>
@@ -1264,7 +1260,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1272,10 +1268,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1373,39 +1369,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1456,7 +1452,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1476,39 +1472,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1559,7 +1555,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1579,17 +1575,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1607,11 +1603,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1620,49 +1616,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1682,17 +1678,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1710,11 +1706,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1765,7 +1761,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1785,10 +1781,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1815,7 +1811,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1866,7 +1862,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1886,10 +1882,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1923,7 +1919,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -1945,7 +1941,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1963,7 +1959,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -1983,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2009,10 +2005,10 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2064,7 +2060,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:09:15+00:00</t>
+    <t>2025-03-05T10:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>custodian</t>
+    <t>CDA - custodian</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T10:03:58+00:00</t>
+    <t>2025-04-22T14:43:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -709,42 +709,42 @@
   <dimension ref="A1:AK13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.8046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.8046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="152.12890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="130.42578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.46484375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.44140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.55078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="24.3828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-22T14:43:59+00:00</t>
+    <t>2025-04-23T09:14:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:14:13+00:00</t>
+    <t>2025-05-19T09:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T09:31:54+00:00</t>
+    <t>2025-05-20T13:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1896,7 +1896,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/main/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
